--- a/output/CLOTH01_summer/feeds_excel/simulation feeds/SupplierReceipts.xlsx
+++ b/output/CLOTH01_summer/feeds_excel/simulation feeds/SupplierReceipts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240401_DC_01_000003</t>
+          <t>PO_CLOTH01_20240401_DC_01_000004</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>1161.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240401_DC_01_000005</t>
+          <t>PO_CLOTH01_20240401_DC_01_000006</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -544,23 +544,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2024-04-08 00:00:00</t>
+          <t>2024-04-09 00:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1767.96</t>
+          <t>1346.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -597,23 +597,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2024-04-09 00:00:00</t>
+          <t>2024-04-13 00:00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_003</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>586.46</t>
+          <t>222.74</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240408_DC_01_000021</t>
+          <t>PO_CLOTH01_20240401_DC_01_000003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -650,23 +650,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>218.7</t>
+          <t>5100.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240408_DC_01_000023</t>
+          <t>PO_CLOTH01_20240401_DC_01_000005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -703,23 +703,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1571.52</t>
+          <t>817.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240408_DC_01_000020</t>
+          <t>PO_CLOTH01_20240408_DC_01_000022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-19 00:00:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1664.48</t>
+          <t>716.68</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240401_DC_01_000003</t>
+          <t>PO_CLOTH01_20240415_DC_01_000039</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-22 00:00:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>540.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240415_DC_01_000039</t>
+          <t>PO_CLOTH01_20240415_DC_01_000038</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -862,23 +862,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1632.96</t>
+          <t>2036.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240415_DC_01_000042</t>
+          <t>PO_CLOTH01_20240415_DC_01_000041</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -915,23 +915,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1407.82</t>
+          <t>587.76</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240415_DC_01_000038</t>
+          <t>PO_CLOTH01_20240408_DC_01_000021</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -968,23 +968,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1433.76</t>
+          <t>14222.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240415_DC_01_000041</t>
+          <t>PO_CLOTH01_20240408_DC_01_000023</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1021,23 +1021,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,63 +1047,10 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>278.32</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GRV_CLOTH01_000012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PO_CLOTH01_20240408_DC_01_000022</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DC_01</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ITM_TOP_0003</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2024-04-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>SUP_001</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1131.9</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
